--- a/Assets/StreamingAssets/Chapter/Chapter2.xlsx
+++ b/Assets/StreamingAssets/Chapter/Chapter2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\shina\Assets\StreamingAssets\Chapter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69FF8545-E163-4F6D-A516-1181E33D37CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122E3B28-988D-4D19-9E78-32A3C791374E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{93CEB1B2-C3AD-4226-8194-AA135A927779}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15390" xr2:uid="{93CEB1B2-C3AD-4226-8194-AA135A927779}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,1309 +38,1297 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="325">
   <si>
+    <t>云叶枫有太空经验，漠寒队员，听说你也有相关履历——</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>以钛科学太空观测站 C区附近 27公里处，出现一群水母状生物。你们的任务是调查事件并带回研究样本。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&amp;VO</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>周文涵</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行过三次太空任务。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>好，我会通知其他人集合，你来会议室一趟。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>所以我们要去太空？真的假的？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶苏明满脸惊讶，眼底却透着掩不住的兴奋。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶苏明</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶苏明队员暂无太空经历。目前已知漠寒和云叶枫有太空任务经验，全队太空经验者过半。因安全等级未知，任务或有危险，我未向上级提交转移申请，你们务必相互照应。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>太空站会有人接应，提供更详细信息。叶枫有飞船驾驶经验，此次由他负责驾驶。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>会议结束，三人到换衣间换上工作服：云叶枫与叶苏明的是黑色，漠寒则为白色。叶苏明的辅色是红与紫，云叶枫为黄，漠寒为蓝。三人右手均戴着灰色手套——</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>还挺壮观。是我俯视世界，还是世界在仰视我？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶苏明拍他后背</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你又不是哲学家，想这些干嘛？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（皱眉）不让人抒发下情感啊？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫似在琢磨漠寒的话</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒一怔</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>好句，我抄了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我写小说。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒动了动耳朵，语气带点调皮</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你上家的飞行器什么样？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>比这大，可能和队伍规模有关。但以钛科学的应该更好——至少不这么挤。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>嗯？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>上家的座位安排，跟坐直升机似的，不知道的还以为要去跳伞！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>FoxTi！飞行器已部署。可以登船了！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>周文涵 ·）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>登上飞行器，云叶枫坐驾驶位，漠寒与叶苏明坐后排。系好安全带、关好舱门后，云叶枫将空调调至 21℃，靠在座位上。漠寒环顾四周，环境还算舒适，像坐私家车一般。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>广播</t>
+  </si>
+  <si>
+    <t>C-750号太空引力推行飞行器已完全部署！执行人员：科考队 FoxTi。飞行时间：2064年 7月 19日，下午 2点 47分 08秒……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒，我有点紧张。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我怎么看不出来？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>广播</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>是吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>引擎发出雷霆般轰鸣，机身却毫无震动。漠寒望向窗外，平台地面浮现一圈紫色正方形光环。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>有种下次不想上太空的感觉……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>那下次不带你了？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你是想看风景，还是想压死我？你那边不也一样？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒这边视野更好。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>是‘漠寒这边好看’，还是‘漠寒好看’？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶苏明的耳朵竖了起来。漠寒透过他的毛发，似乎感觉到他脸颊微红——或许是错觉，但确实觉得他身上有点热。</t>
+  </si>
+  <si>
+    <t>没、没有——</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>真的？（嘴角微扬）看着不像啊。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>窗外，地平线上泛起蓝色光晕，将天地分割成明暗两面。三人渐感失重，想来飞船开始减速。五分钟后，飞行器进入预定轨道。脚下的地球反射着太阳光，将舱内染成蓝色；远方的太阳化作亮斑，与百万繁星一同注视着他们。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶苏明指向窗外</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>真像别人说的——像个狗头。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>哪？瑞州在南海，面积再大也看不到啊。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>咱们家乡太吸引我了，隔了地平线我也能‘看’到。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>半年多。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>——你们多久没回家了？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不像你能天天回。我也有两三个月了——队长，还不开车？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动驾驶呢。这种事还轮不到我。不如聊聊？我也好了解你们。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>啊……云叶枫，你回家都做什么？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>照顾我妈，和我爸一起。这也是我在这的原因——好好工作，和我爸一起筹钱给我妈治病。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这样啊……你也是……挺辛苦了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫察觉气氛沉重，主动带笑</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>唉，别这么严肃！我妈又不是没救了，而且我们还有希望。对了，你们为什么干这行？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>回想起考博那天，因给车祸伤者做心肺复苏迟到十分钟，最后一题少求一个解，与博士学位差了0.5分——漠寒正怔忡，却与叶苏明同时开口，又同时闭嘴。叶苏明用眼神示意他先说。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我嘛……从小就被以钛吸引，想揭开它的神秘面纱。无奈脑子不够，进不了实验室。或许是爱好拉了后腿吧。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>喂！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶苏明眯眼看向漠寒</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你上次考博不是哭着说差点就成了吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>那也超过很多人了。后悔吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>怎么会。（笑了笑）以科考员身份探索以钛，也算走在梦想路上了。哦——叶苏明，你呢？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我吗？（突然笑起来）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>两人等着他的答案，叶苏明却只顾着笑。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>太远，闻不到味。（眯眼，嘴角上扬）这不，你一回国我就嗅到了，还推荐你来以钛科学了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>FoxTi已被接应，可以出舱了！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>FoxTi，任务更新：先前往太空站中心区，有人会说明任务需求。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>走喽！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>途中经过太空花园，里面百花盛开，温度适宜，有小机器人打理。假山怪石嶙峋，两侧桃花盛放，如小姑娘的发卡；花坛里的迎春花星星点点，似瀑布上镶嵌的宝石。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨大的蓝色星球与璀璨群星一同“观赏”着这片祥和之地，其间却透着生命的野心与生机。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶苏明突然停下，漠寒与云叶枫也随之驻足。漠寒凑到他身边，一同望着花草；云叶枫本想催促，又觉机会难得，便用手表倒计时一分钟，嘱咐两人别耽误太久，自己也索性赏玩起来。三人在花园里逛了一圈，心情轻快。计时结束，才继续赶路。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>抵达空间站中心区舱门，门上有体位示意图，示意进入者需平躺。漠寒、叶苏明与云叶枫抓住把手，脚朝指定区域。舱门关闭后，一股推力传来，随之是重力感。他们站起身时，叶苏明跳了一下，差点撞到舱顶——好在没太用力。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>重力？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>离心力。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>舱门再次打开，露出设备齐全的实验室。中央是环形实验桌，摆满试管、烧杯等玻璃器皿；一侧是运转的检测仪器，角落的巨大计算机占了整面墙，屏幕滚动着代码与图表。环形桌内站着一位蓝白色龙人。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>他是空间站管理人员，也是以钛科学研究以钛的主席之一。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>FoxTi？我是观测站站长，现在说明情况。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>龙人</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫上前握手，龙人理了理大褂</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>他从桌上拿起一个类似枪的物件，弹匣是巴掌大的透明容器：</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫接过工具，三人转身离开时，见龙人正注视着房间一侧的大屏幕。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>顺带说一句——那里的虚空场已经达到最低解体标准。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>去过不少地方，还有世界之外（自豪）。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>话说漠寒，除了太空还去过哪？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒点头，不愿多谈</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>相比其他虚空，瑞州虚空算最和谐的了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>等等，怎么突然聊这么高深的？空间投影区到底是什么？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>就是……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞行器窗的外边是一群水母群，丝丝缠绕的月形水母伴随着星空浪翩翩舞，这一幕看上去好像是水母在地球的表面上遨游。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这些水母一群又一群，漫无目的，偶尔又聚聚在一起，像是在讨论一些什么。或许，他们在对这一群外人窃窃私语，议论他们来自哪里，来自何方国度。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>隐约间，一些气泡从飞行器的窗外掠过——似乎他们在海洋里，地球是一个巨大的细胞，将它代谢出来的气体排出。这些水母玩弄着这些气泡，直至气泡裂开，他们才心灰意冷的离开。他们就像是刚出生的幼童一样，好奇，大胆，昼夜不停地探索这个世界。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这些就是目标？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>嗯。开始行动吧。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>好可爱……就对付这些？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶苏明 ·）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>看着可爱，未知才最可怕。注意安全。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫 ·）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>出舱后，他们先勘探空间数值：各项指标正常，唯有这群水母是异常。云叶枫用钳子抓住一只小水母，它在钳头容器里上蹿下跳，只顾逃脱，毫无攻击行为。他摇晃容器轻微刺激，水母依旧只想着逃。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>样本枪带了吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>为什么现在有攻击行为？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒盯着水母，心中疑窦丛生，犹豫着是否说出想法——怕观点不够严谨。但他笃定，水母的攻击定是因生命受威胁。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>周文涵指挥官，FoxTi任务完成！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这就完了？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>是！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>三人返回飞行器，漠寒与叶苏明刚进舱门，飞船突然被撞击，开始旋转。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>情况有变！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>耳机里传来云叶枫的大喊，他手中的样本枪恰好被丢进舱内。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒与叶苏明冲出舱门，只见一只体型是云叶枫五倍的水母，正用触手捆着他往远离飞行器的方向游，水母“帽子”散发着紫色光芒。二人来不及多想，立刻追上去。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>几番挣扎无果，云叶枫对着漠寒和叶苏明大喊：</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>视觉强化！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒 ·）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒立刻提醒叶苏明。眼前浮现几道边框，视野骤清，自动放大锁定云叶枫。他飞向云叶枫，叶苏明开启视觉强化紧随其后。叶苏明突然察觉，自己眨眼时竟毫无视觉中断感。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>追逐间，一团黄色能量从云叶枫身旁爆开，大水母松开触手。云叶枫愣住了，漠寒与叶苏明也傻眼——云叶枫不是不会用元核吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒反应过来，飞过去将云叶枫护在身下；云叶枫看着“元钛隔膜耐久：0%”的提示，缓缓长叹。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>三人有惊无险回到飞行器后舱，舱门关闭，蓝色屏障扫过停在门口。叶苏明和云叶枫脱去宇航服，云叶枫返回驾驶位时，漠寒却再次向外走去。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶苏明拉住他，凝视着他的眼睛。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我去求证件事，马上回来。（拨开手）我不会有事。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>果然……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒求证完毕，返回舱内。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我感觉我像是死了一次。吓出心脏病了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>有这么严重？你的大心脏呢？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>说话时，漠寒察觉到他指尖微颤——比起云叶枫，叶苏明显得更紧张。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>开玩笑的！（转向漠寒）漠寒，谢了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>好了好了。云叶枫，介意我来写任务报告吗？以钛科学应该也需要这个吧？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫一愣，随即点头：</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>真的？可是，为什么？没看出你对这个有兴趣。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（含蓄一笑）关于这些水母，我有些发现，我来写更合适。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>什么发现？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这群水母喜好元钛环境，厌恶虚空环境，就这么简单。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫看向自己的手套，瞳孔骤缩，细思极恐。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>置换时，它受到了本地虚空场影响，所以躁动。后来安静，是因为太空服的元钛隔膜覆盖了它——对了，介意明天我教你用元核吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>元核？怎么说？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我看到你用了元核。那团橙色的光。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你说那个爆炸？真是元核弄的？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>是啊！我用元核几百年了，还能看不出来？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（小声）原来不是手套突然管用了……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>返回太空站，将水母交给中央实验室的龙人后，三人向周文涵申请逗留，获允后直奔太空花园。先合影留念，再各自闲逛。因时间充裕，他们见到了反重力喷泉、人工小湖……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒和叶苏明飞过去撸狗，云叶枫却在摆弄手机。漠寒凑过去，见他在给母亲发消息，内容有水母照片、星空景象、月球模样……其中一句是：“妈，好点了吗？”</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>是阿姨让你发的，还是你自己想发？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒在花园拍了些风景，既作纪念也积累素材，还像云叶枫那样发给父母。关屏后，他望向星空之外——科学称那是虚空。可虚空之外呢？没有答案——</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>无限本就是人类难以理解的概念，无法超越认知局限去验证。人类在宇宙中的位置？宇宙是否有目的？若有，人为何而活？若无，人又为何存在？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒常想这些，此刻却有了答案——为了存在而存在。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶苏明不知何时凑过来</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>想什么？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>哲学问题，不过不重要——不撸狗了？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（摇头）它的狗头哪有你的好摸？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不行吗？（眯眼调戏）作为交换，我让你摸回来。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒吸了口气，额头抵着大玻璃窗，略带不好意思：</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶苏明的耳朵突然立起，兴奋</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>随便说说你就同意了？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>并非随便……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>好吧……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>相机</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒动了动耳朵，猛地回头，见云叶枫正拿手机拍他们。他一巴掌轻轻拍在叶苏明脑门上，随即朝云叶枫飞去。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不删，也不发——纯留着报复你们。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>嗯哼？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>搞得我像个外人。（带着略微阴险的笑）这样吧——帮你们记录一下你们的生活。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶苏明也飞过来</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫你听我狡辩——我们绝对是正常的朋友。只要你发我一份我保证这事情就跟你没有什么关系了！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒点了点头，突然，他好像反应过来了什么东西，又猛猛摇头。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫回答了一声“好”，然后当着两人的面把图片分享给了叶苏明，接着删除了图片和发送的聊天记录。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒抱臂叹气</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>goChapter &gt;&gt; story.第三章</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>addTag &gt;&gt; 解锁第二章</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;◤2064年 7月 19日</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Black</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效/电话震动</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒正在训练室研究以钛科学的装备。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器库_TAS</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>淡入</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>他看向柜子里的元钛联动制式手枪——与世界蛇款型相似，只是扳机处刻着以钛科学的徽标。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>会议室_TAS</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>全员聚齐，周文涵开始向 FoxTi阐明任务细节。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑场</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;淡入&gt;&lt;中心文本&gt;下午 2点 21分</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效/车子行驶而过</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&amp;Scene</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>太空水母/俯视城市</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>或许，我们看世界时，世界也在看我们。世界本就是每个人的舞台。我们做的，就是出演好自己的角色。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>随口说的能被用进你的小说，挺荣幸——写完给我看看？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>太空发射站_TAS</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫&amp;叶苏明</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效/连接成功1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>太空水母/飞行器前</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>太空水母/飞行器前_2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶苏明的手不自觉贴在漠寒大腿外侧。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>——</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>三人进入大楼，才发现内部呈凹陷状，过道从一侧工作区连接至另一侧。中央是金属平台，台面下布有线路。片刻后，一辆箭头状飞行器从凹陷处飞来，底边四角及反向底面两角各有蓝色正方形投影——这是引力驱动飞行器，距地面约半米。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞行器降在平台中央，几个小型飞行机器人环绕扫描。三人登上平台，等待部署完毕。近看飞行器，车头棱角分明，内外均为黑白黄配色，黄色为主调。内部有四个座位，驾驶位旁一个，后排两个，还带一个车库。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>太空水母/太空_太空站的路上</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>太空水母/太空站外观</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞行器进入空间站的凹口，吸附在地板上。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>太空水母/太空站外观_无飞船</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效/泄压放气</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效/机械门开启1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫率先推门，其余两人跟上。他们的脚步与手套均发出蓝色圆圈投影，投影方向的反方向是他们受力的运动方向。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>从飞行器暂存仓出来，眼前是明亮的灯光与过道，简约干净，标有位置标识与名称。云叶枫抬手，手表投影出地图与方向指示，中央有个黄色标识。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>太空水母/抵达空间站</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>太空水母/太空花园</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效/太空花园</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>太空水母/太空站中心</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>返回飞行器，各自坐好。舱门打开，漫天繁星再次映入眼帘。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞船弹射出去，云叶枫手动驾驶，因距任务点还有几公里，便闲聊起来。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;云叶枫便简单解释了一番。说话间，已抵任务点。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>太空水母/太空水母1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>太空水母/太空水母2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶苏明缓缓松开，在窗边静静注视。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒飞向附近的水母群，手上聚集元钛，散出蓝色微粒。水母如饿狼般涌向他的手，似在舔舐什么一样。他移动手，水母也随之跟上。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>太空水母/太空水母3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效/拍照1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;随后，三人像没事人一样，在花园里坐着玩了会儿游戏。一小时后，不舍地返回飞行器，驶入预设轨道。自动驾驶中，他们望向窗外——星空渐淡，蓝天重现，陆地轮廓愈发清晰……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;他们如同沧海一粟，寄蜉蝣于天地，驾一叶之扁舟，却载着满舱的鲜活与希望。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫扫过队员——叶苏明尤其亢奋。虽知他练过太空机动设备，作为队长仍难免担心其粗心毛病。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>‘抄’？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我这文笔恐怕你看不下去。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>图个乐，没关系。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>行，工作完再说。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效/风弹_短</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>5g超重训练你又不是没做过。放心，加速时间不长。到了太空，会舒服多。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒盯着叶苏明，见他面露不适，使劲把手搭在叶苏明的肩上。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>三十多秒后，叶苏明才缓过来，有些瘫软地坐在座位上，长舒一口气</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（立刻坐好）开玩笑的！我当然想上！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你们关系是真好，感觉我像个外人。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我是因为……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶苏明好不容易绷住脸，想正经说，却又笑了出来</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>因为漠寒太吸引我了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>舱内一时寂静，漠寒与云叶枫仿佛“死机”。突然，云叶枫大笑，一言不发，好奇漠寒会说些什么。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你他妈——（拍着大腿）那你怎么不来世界蛇？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>正经一点。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒盯着叶苏明的眼睛。叶苏明下意识回避，接着有些支吾</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>讨口饭吃嘛……反正……就是……之前听到漠寒你干这一行，所以我也混进这一行了……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不必，路上我和他们解释就好了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>带回几只小水母即可，我们需查明其属性。任务坐标已更新到飞行器上，可稍作休整再出发。还有——</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒心头一震，脑海中闪过苏格兰岛事件的记忆碎片。云叶枫看漠寒在发愣，关心地问是否有哪里不适。漠寒只是摇了摇头。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>三人到飞行器仓库换上轻便宇航服，检查气密性后，云叶枫按下出舱按钮。一道蓝色屏障扫过他们，隔绝了声音。漠寒回头，见屏障停在仓库的后方。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶苏明飞过来，递过置换枪。云叶枫接过枪，把水母装入容器，松开钳子。水母迅速反应，快速挣脱。云叶枫再次用钳子去夹，被水母躲过。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我来帮你。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶苏明拿过云叶枫手中的钳子。这时，漠寒飞了过来。叶苏明看了眼漠寒，二话不说就把钳子塞到漠寒手里。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>哈？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你来，毕竟你刚入队嘛，我和云叶枫磨合地差不多了。（搓手）你们两磨合一下。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒看了眼云叶枫，云叶枫微笑着点点头，带着漠寒去找另外一些水母。奇怪的是，所有水母开始对钳子有闪避行为。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>它们灵活地像无形的风，怎么抓也抓不住。要么掠过钳头，要么窜出容器，要么一开始就躲得远远的……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>要不我来？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫和漠寒交换工具。令云叶枫遗憾的是，他也抓不了一只。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒摇摇头，再次和云叶枫交换工具。一只水母游过漠寒的右肩膀，漠寒快速伸手，手中出现青蓝色粒子。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>水母好似被吸附一般固定在漠寒的掌心下，为了保证安全，漠寒可以让水母和手掌隔开了点距离。于是，水母如婴儿般被放入了容器中。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>没等水母反应，云叶枫按下按钮。突然，水母剧烈挣扎，展现出攻击行为，撞得容器晃动。云叶枫手一抖——多半是被水母撞的。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>几秒后，水母平静下来，仿佛什么都没发生。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶苏明飞了过来，手上抱着刚从飞行器中拿出的另外几个容器。云叶枫将置换枪中的容器卸下，容器被自动封口。重复操作后，三人共捕获八只水母。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶苏明意犹未尽。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>做得很好。现在带回样本。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫本想通过手套瞬移到他们身边，却发现电量与元钛储备莫名耗尽——明明下船前检查过。他用力掰扯触手，却纹丝不动；再看太空服数据，元钛隔膜耐久与电力都在流失——云叶枫怀疑是这大只水母干的，这水母似乎突破了投影区规则限制。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>耳机里只传来“视觉”二字，叶苏明一脸茫然，漠寒的耳朵却在毫秒内竖起，背后沁出冷汗。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>因水母轨迹难测，二人不敢用武器，怕误伤云叶枫。终于追上，云叶枫伸手，漠寒尝试抓住时却脱了手。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>大水母游至投影区边缘，渐渐消失。漠寒返程时，见一群小水母游向爆炸点，心中有了猜测。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>可我们捕获时，他们在元钛场里异常躁动。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>说完，云叶枫启动自动驾驶</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶苏明，帮我盯着外面——我现在好困……不知道为什么……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒也困，他知道困的原因——虚空场强下元核使用元钛的量比在正常情况下多。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒不自觉地把眼睛眯上。叶苏明扫视两人，从后座爬到副驾驶，安静地盯着前方和表盘数据。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>偶然发现一只浮在空中的小土狗，脖子戴黑项圈，项圈上写着“混合意识流实验体-1”，脚穿白“鞋”，飞行自如，显然训练有素。小狗见人便摇尾巴，像个螺旋桨。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫见漠寒过来，把手机稍挪向漠寒</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>就想让她也看看世界。我看到的美好，她也该看看。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒没说话，轻轻拍了拍他的肩，转身飞向叶苏明——他看见云叶枫眼眶微红，许是需要独处。云叶枫望着他的背影，神色忧郁。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不是，（皱眉）你想摸我头？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>都这么大了，感觉你一点没变。摸吧摸吧。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶苏明试探着把手放在漠寒头上，轻轻抚过。漠寒眯着眼睛，有些无聊。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait &gt;&gt; 4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒惬意地看向窗外。地面景物逐渐缩小，只剩一片蓝天与大地。天色渐暗时，一颗流星划过，留下轨迹，三人不约而同望向窗外。叶苏明看得入神，甚至压在漠寒身上，一手扶窗，紧盯着外面。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>太空水母/漠寒看窗外</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音乐/落日余晖</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait &gt;&gt; 2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（愣）不是？你也来？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效/对讲机噪声</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;抵磁器已就绪——</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;磁力推进器已就绪——</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;三！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;二！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;一瞬间，飞行器如弹弓射出的石子般蹿出。三人顿时感受到强烈的超重感。叶苏明本想说什么，却被推力噎住，只发出一声“唔”。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;——</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;弹簧引擎成功将飞行器抛出！加速度 4.1g……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音乐/The Dragon Fell in Love with The Knight</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫看向窗外，飞行器开始减速。几分钟后，飞船靠近空间站。透过玻璃可见过道内的绿植。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁档案 &gt;&gt; 投影区</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁档案 &gt;&gt; 瑞州</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁档案 &gt;&gt; 瑞州虚空</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这是样本空间投影点置换枪，自带元钛，可在容器中制造强元钛场，方便你们取样。另外，工作人员刚在你们的飞行器中放了额外的取样容器，尽量多抓点。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这是放大元核效应或引导元核的装置，由&lt;link=profile:[*]元钛&gt;元钛&lt;/link&gt;驱动，仅元核使用者可佩戴使用。唯独云叶枫的手套特殊，有纹路似的线路贴合到皮肤表面。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒！看见&lt;link=profile:[*]瑞州 | [*]兽人&gt;瑞州&lt;/link&gt;了吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这次任务应较安全，不必紧张。任务点的‘水母’实际是其他空间的投影——那片区域是‘被&lt;link=profile:[*]投影区&gt;空间投影区&lt;/link&gt;’——需要解释么？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>世界之外？虚空？我只去过几次&lt;link=profile:[*]瑞州虚空&gt;瑞州虚空&lt;/link&gt;。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效/早晨白噪音|音乐/When The Wind Blows</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音乐/Airport Lounge</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音乐/Organic Meditations Three</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音乐/Half Mystery</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>界面抖动</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒，你说为什么同一座城市，隔了一条河样子就完全不一样啊？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>因为我们现在在郊区。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不止这一点吧？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>为了优化空气质量，政府在火灵这座城市中建造了不少小型或大型绿化区。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>原来是这样……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶苏明听着鸟语，深吸一口气，空气中有着淡淡花香。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫说着，不经意间流露出自豪的神情。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>在我小时候……我经常看见雾霾。但现在没有了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫远眺，脸上勾出一抹笑。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效/对讲机打开</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>noti &gt;&gt; 已进入近地轨道 &gt;&gt; C-750 &gt;&gt; 3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>人物</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>对话</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>语音</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>背景/cg</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>背景音乐</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>转场特效</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>立绘</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>立绘层</t>
   </si>
   <si>
     <t>对话框头像</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>#TAG</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>选项</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>QTE</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>TE. HUD层</t>
   </si>
   <si>
     <t>指令</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫有太空经验，漠寒队员，听说你也有相关履历——</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>以钛科学太空观测站 C区附近 27公里处，出现一群水母状生物。你们的任务是调查事件并带回研究样本。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&amp;VO</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>周文涵</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>执行过三次太空任务。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>好，我会通知其他人集合，你来会议室一趟。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>所以我们要去太空？真的假的？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明满脸惊讶，眼底却透着掩不住的兴奋。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明队员暂无太空经历。目前已知漠寒和云叶枫有太空任务经验，全队太空经验者过半。因安全等级未知，任务或有危险，我未向上级提交转移申请，你们务必相互照应。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>太空站会有人接应，提供更详细信息。叶枫有飞船驾驶经验，此次由他负责驾驶。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>会议结束，三人到换衣间换上工作服：云叶枫与叶苏明的是黑色，漠寒则为白色。叶苏明的辅色是红与紫，云叶枫为黄，漠寒为蓝。三人右手均戴着灰色手套——</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>还挺壮观。是我俯视世界，还是世界在仰视我？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明拍他后背</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>你又不是哲学家，想这些干嘛？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>（皱眉）不让人抒发下情感啊？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫似在琢磨漠寒的话</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒一怔</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>好句，我抄了。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我写小说。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒动了动耳朵，语气带点调皮</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>你上家的飞行器什么样？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>比这大，可能和队伍规模有关。但以钛科学的应该更好——至少不这么挤。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>嗯？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>上家的座位安排，跟坐直升机似的，不知道的还以为要去跳伞！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>FoxTi！飞行器已部署。可以登船了！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>周文涵 ·）</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>登上飞行器，云叶枫坐驾驶位，漠寒与叶苏明坐后排。系好安全带、关好舱门后，云叶枫将空调调至 21℃，靠在座位上。漠寒环顾四周，环境还算舒适，像坐私家车一般。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>广播</t>
-  </si>
-  <si>
-    <t>C-750号太空引力推行飞行器已完全部署！执行人员：科考队 FoxTi。飞行时间：2064年 7月 19日，下午 2点 47分 08秒……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒，我有点紧张。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我怎么看不出来？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>广播</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>是吗？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>引擎发出雷霆般轰鸣，机身却毫无震动。漠寒望向窗外，平台地面浮现一圈紫色正方形光环。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>有种下次不想上太空的感觉……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>那下次不带你了？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>你是想看风景，还是想压死我？你那边不也一样？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒这边视野更好。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>是‘漠寒这边好看’，还是‘漠寒好看’？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明的耳朵竖了起来。漠寒透过他的毛发，似乎感觉到他脸颊微红——或许是错觉，但确实觉得他身上有点热。</t>
-  </si>
-  <si>
-    <t>没、没有——</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>真的？（嘴角微扬）看着不像啊。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>窗外，地平线上泛起蓝色光晕，将天地分割成明暗两面。三人渐感失重，想来飞船开始减速。五分钟后，飞行器进入预定轨道。脚下的地球反射着太阳光，将舱内染成蓝色；远方的太阳化作亮斑，与百万繁星一同注视着他们。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明指向窗外</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>真像别人说的——像个狗头。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>哪？瑞州在南海，面积再大也看不到啊。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>咱们家乡太吸引我了，隔了地平线我也能‘看’到。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>半年多。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>——你们多久没回家了？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>不像你能天天回。我也有两三个月了——队长，还不开车？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>自动驾驶呢。这种事还轮不到我。不如聊聊？我也好了解你们。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>啊……云叶枫，你回家都做什么？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>照顾我妈，和我爸一起。这也是我在这的原因——好好工作，和我爸一起筹钱给我妈治病。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>这样啊……你也是……挺辛苦了。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫察觉气氛沉重，主动带笑</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>唉，别这么严肃！我妈又不是没救了，而且我们还有希望。对了，你们为什么干这行？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>回想起考博那天，因给车祸伤者做心肺复苏迟到十分钟，最后一题少求一个解，与博士学位差了0.5分——漠寒正怔忡，却与叶苏明同时开口，又同时闭嘴。叶苏明用眼神示意他先说。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我嘛……从小就被以钛吸引，想揭开它的神秘面纱。无奈脑子不够，进不了实验室。或许是爱好拉了后腿吧。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>喂！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明眯眼看向漠寒</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>你上次考博不是哭着说差点就成了吗？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>那也超过很多人了。后悔吗？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>怎么会。（笑了笑）以科考员身份探索以钛，也算走在梦想路上了。哦——叶苏明，你呢？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我吗？（突然笑起来）</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>两人等着他的答案，叶苏明却只顾着笑。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>太远，闻不到味。（眯眼，嘴角上扬）这不，你一回国我就嗅到了，还推荐你来以钛科学了。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>FoxTi已被接应，可以出舱了！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>FoxTi，任务更新：先前往太空站中心区，有人会说明任务需求。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>走喽！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>途中经过太空花园，里面百花盛开，温度适宜，有小机器人打理。假山怪石嶙峋，两侧桃花盛放，如小姑娘的发卡；花坛里的迎春花星星点点，似瀑布上镶嵌的宝石。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>巨大的蓝色星球与璀璨群星一同“观赏”着这片祥和之地，其间却透着生命的野心与生机。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明突然停下，漠寒与云叶枫也随之驻足。漠寒凑到他身边，一同望着花草；云叶枫本想催促，又觉机会难得，便用手表倒计时一分钟，嘱咐两人别耽误太久，自己也索性赏玩起来。三人在花园里逛了一圈，心情轻快。计时结束，才继续赶路。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>抵达空间站中心区舱门，门上有体位示意图，示意进入者需平躺。漠寒、叶苏明与云叶枫抓住把手，脚朝指定区域。舱门关闭后，一股推力传来，随之是重力感。他们站起身时，叶苏明跳了一下，差点撞到舱顶——好在没太用力。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>重力？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>离心力。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>舱门再次打开，露出设备齐全的实验室。中央是环形实验桌，摆满试管、烧杯等玻璃器皿；一侧是运转的检测仪器，角落的巨大计算机占了整面墙，屏幕滚动着代码与图表。环形桌内站着一位蓝白色龙人。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>他是空间站管理人员，也是以钛科学研究以钛的主席之一。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>FoxTi？我是观测站站长，现在说明情况。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>龙人</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫上前握手，龙人理了理大褂</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>他从桌上拿起一个类似枪的物件，弹匣是巴掌大的透明容器：</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫接过工具，三人转身离开时，见龙人正注视着房间一侧的大屏幕。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>顺带说一句——那里的虚空场已经达到最低解体标准。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>去过不少地方，还有世界之外（自豪）。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>话说漠寒，除了太空还去过哪？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒点头，不愿多谈</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>相比其他虚空，瑞州虚空算最和谐的了。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>等等，怎么突然聊这么高深的？空间投影区到底是什么？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>就是……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>飞行器窗的外边是一群水母群，丝丝缠绕的月形水母伴随着星空浪翩翩舞，这一幕看上去好像是水母在地球的表面上遨游。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>这些水母一群又一群，漫无目的，偶尔又聚聚在一起，像是在讨论一些什么。或许，他们在对这一群外人窃窃私语，议论他们来自哪里，来自何方国度。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>隐约间，一些气泡从飞行器的窗外掠过——似乎他们在海洋里，地球是一个巨大的细胞，将它代谢出来的气体排出。这些水母玩弄着这些气泡，直至气泡裂开，他们才心灰意冷的离开。他们就像是刚出生的幼童一样，好奇，大胆，昼夜不停地探索这个世界。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>这些就是目标？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>嗯。开始行动吧。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>好可爱……就对付这些？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明 ·）</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>看着可爱，未知才最可怕。注意安全。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫 ·）</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>出舱后，他们先勘探空间数值：各项指标正常，唯有这群水母是异常。云叶枫用钳子抓住一只小水母，它在钳头容器里上蹿下跳，只顾逃脱，毫无攻击行为。他摇晃容器轻微刺激，水母依旧只想着逃。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>样本枪带了吗？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>为什么现在有攻击行为？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒盯着水母，心中疑窦丛生，犹豫着是否说出想法——怕观点不够严谨。但他笃定，水母的攻击定是因生命受威胁。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>周文涵指挥官，FoxTi任务完成！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>这就完了？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>是！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>三人返回飞行器，漠寒与叶苏明刚进舱门，飞船突然被撞击，开始旋转。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>情况有变！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>耳机里传来云叶枫的大喊，他手中的样本枪恰好被丢进舱内。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒与叶苏明冲出舱门，只见一只体型是云叶枫五倍的水母，正用触手捆着他往远离飞行器的方向游，水母“帽子”散发着紫色光芒。二人来不及多想，立刻追上去。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>几番挣扎无果，云叶枫对着漠寒和叶苏明大喊：</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>视觉强化！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒 ·）</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒立刻提醒叶苏明。眼前浮现几道边框，视野骤清，自动放大锁定云叶枫。他飞向云叶枫，叶苏明开启视觉强化紧随其后。叶苏明突然察觉，自己眨眼时竟毫无视觉中断感。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>追逐间，一团黄色能量从云叶枫身旁爆开，大水母松开触手。云叶枫愣住了，漠寒与叶苏明也傻眼——云叶枫不是不会用元核吗？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒反应过来，飞过去将云叶枫护在身下；云叶枫看着“元钛隔膜耐久：0%”的提示，缓缓长叹。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>三人有惊无险回到飞行器后舱，舱门关闭，蓝色屏障扫过停在门口。叶苏明和云叶枫脱去宇航服，云叶枫返回驾驶位时，漠寒却再次向外走去。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明拉住他，凝视着他的眼睛。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我去求证件事，马上回来。（拨开手）我不会有事。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>果然……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒求证完毕，返回舱内。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我感觉我像是死了一次。吓出心脏病了。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>有这么严重？你的大心脏呢？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>说话时，漠寒察觉到他指尖微颤——比起云叶枫，叶苏明显得更紧张。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>开玩笑的！（转向漠寒）漠寒，谢了。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>好了好了。云叶枫，介意我来写任务报告吗？以钛科学应该也需要这个吧？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫一愣，随即点头：</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>真的？可是，为什么？没看出你对这个有兴趣。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>（含蓄一笑）关于这些水母，我有些发现，我来写更合适。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>什么发现？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>这群水母喜好元钛环境，厌恶虚空环境，就这么简单。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫看向自己的手套，瞳孔骤缩，细思极恐。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>置换时，它受到了本地虚空场影响，所以躁动。后来安静，是因为太空服的元钛隔膜覆盖了它——对了，介意明天我教你用元核吗？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>元核？怎么说？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我看到你用了元核。那团橙色的光。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>你说那个爆炸？真是元核弄的？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>是啊！我用元核几百年了，还能看不出来？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>（小声）原来不是手套突然管用了……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>返回太空站，将水母交给中央实验室的龙人后，三人向周文涵申请逗留，获允后直奔太空花园。先合影留念，再各自闲逛。因时间充裕，他们见到了反重力喷泉、人工小湖……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒和叶苏明飞过去撸狗，云叶枫却在摆弄手机。漠寒凑过去，见他在给母亲发消息，内容有水母照片、星空景象、月球模样……其中一句是：“妈，好点了吗？”</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>是阿姨让你发的，还是你自己想发？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒在花园拍了些风景，既作纪念也积累素材，还像云叶枫那样发给父母。关屏后，他望向星空之外——科学称那是虚空。可虚空之外呢？没有答案——</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>无限本就是人类难以理解的概念，无法超越认知局限去验证。人类在宇宙中的位置？宇宙是否有目的？若有，人为何而活？若无，人又为何存在？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒常想这些，此刻却有了答案——为了存在而存在。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明不知何时凑过来</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>想什么？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>哲学问题，不过不重要——不撸狗了？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>（摇头）它的狗头哪有你的好摸？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>不行吗？（眯眼调戏）作为交换，我让你摸回来。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒吸了口气，额头抵着大玻璃窗，略带不好意思：</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明的耳朵突然立起，兴奋</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>随便说说你就同意了？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>并非随便……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>好吧……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>相机</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒动了动耳朵，猛地回头，见云叶枫正拿手机拍他们。他一巴掌轻轻拍在叶苏明脑门上，随即朝云叶枫飞去。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>不删，也不发——纯留着报复你们。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>嗯哼？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>搞得我像个外人。（带着略微阴险的笑）这样吧——帮你们记录一下你们的生活。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明也飞过来</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫你听我狡辩——我们绝对是正常的朋友。只要你发我一份我保证这事情就跟你没有什么关系了！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒点了点头，突然，他好像反应过来了什么东西，又猛猛摇头。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫回答了一声“好”，然后当着两人的面把图片分享给了叶苏明，接着删除了图片和发送的聊天记录。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒抱臂叹气</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>goChapter &gt;&gt; story.第三章</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>addTag &gt;&gt; 解锁第二章</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;◤2064年 7月 19日</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Black</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音效/电话震动</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒正在训练室研究以钛科学的装备。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器库_TAS</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>淡入</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>他看向柜子里的元钛联动制式手枪——与世界蛇款型相似，只是扳机处刻着以钛科学的徽标。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>会议室_TAS</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>全员聚齐，周文涵开始向 FoxTi阐明任务细节。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>黑场</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;淡入&gt;&lt;中心文本&gt;下午 2点 21分</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音效/车子行驶而过</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&amp;Scene</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>None</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>太空水母/俯视城市</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>或许，我们看世界时，世界也在看我们。世界本就是每个人的舞台。我们做的，就是出演好自己的角色。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>随口说的能被用进你的小说，挺荣幸——写完给我看看？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>太空发射站_TAS</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫&amp;叶苏明</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音效/连接成功1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>太空水母/飞行器前</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>太空水母/飞行器前_2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明的手不自觉贴在漠寒大腿外侧。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>——</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>三人进入大楼，才发现内部呈凹陷状，过道从一侧工作区连接至另一侧。中央是金属平台，台面下布有线路。片刻后，一辆箭头状飞行器从凹陷处飞来，底边四角及反向底面两角各有蓝色正方形投影——这是引力驱动飞行器，距地面约半米。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>飞行器降在平台中央，几个小型飞行机器人环绕扫描。三人登上平台，等待部署完毕。近看飞行器，车头棱角分明，内外均为黑白黄配色，黄色为主调。内部有四个座位，驾驶位旁一个，后排两个，还带一个车库。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>太空水母/太空_太空站的路上</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>太空水母/太空站外观</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>飞行器进入空间站的凹口，吸附在地板上。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>太空水母/太空站外观_无飞船</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音效/泄压放气</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音效/机械门开启1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫率先推门，其余两人跟上。他们的脚步与手套均发出蓝色圆圈投影，投影方向的反方向是他们受力的运动方向。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>从飞行器暂存仓出来，眼前是明亮的灯光与过道，简约干净，标有位置标识与名称。云叶枫抬手，手表投影出地图与方向指示，中央有个黄色标识。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>太空水母/抵达空间站</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>太空水母/太空花园</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音效/太空花园</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>太空水母/太空站中心</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>返回飞行器，各自坐好。舱门打开，漫天繁星再次映入眼帘。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>飞船弹射出去，云叶枫手动驾驶，因距任务点还有几公里，便闲聊起来。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;云叶枫便简单解释了一番。说话间，已抵任务点。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>太空水母/太空水母1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>太空水母/太空水母2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明缓缓松开，在窗边静静注视。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒飞向附近的水母群，手上聚集元钛，散出蓝色微粒。水母如饿狼般涌向他的手，似在舔舐什么一样。他移动手，水母也随之跟上。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>太空水母/太空水母3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音效/拍照1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;随后，三人像没事人一样，在花园里坐着玩了会儿游戏。一小时后，不舍地返回飞行器，驶入预设轨道。自动驾驶中，他们望向窗外——星空渐淡，蓝天重现，陆地轮廓愈发清晰……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;他们如同沧海一粟，寄蜉蝣于天地，驾一叶之扁舟，却载着满舱的鲜活与希望。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫扫过队员——叶苏明尤其亢奋。虽知他练过太空机动设备，作为队长仍难免担心其粗心毛病。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>‘抄’？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我这文笔恐怕你看不下去。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>图个乐，没关系。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>行，工作完再说。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音效/风弹_短</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>5g超重训练你又不是没做过。放心，加速时间不长。到了太空，会舒服多。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒盯着叶苏明，见他面露不适，使劲把手搭在叶苏明的肩上。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>三十多秒后，叶苏明才缓过来，有些瘫软地坐在座位上，长舒一口气</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>（立刻坐好）开玩笑的！我当然想上！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>你们关系是真好，感觉我像个外人。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我是因为……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明好不容易绷住脸，想正经说，却又笑了出来</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>因为漠寒太吸引我了。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>舱内一时寂静，漠寒与云叶枫仿佛“死机”。突然，云叶枫大笑，一言不发，好奇漠寒会说些什么。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>你他妈——（拍着大腿）那你怎么不来世界蛇？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>正经一点。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒盯着叶苏明的眼睛。叶苏明下意识回避，接着有些支吾</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>讨口饭吃嘛……反正……就是……之前听到漠寒你干这一行，所以我也混进这一行了……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>不必，路上我和他们解释就好了。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>带回几只小水母即可，我们需查明其属性。任务坐标已更新到飞行器上，可稍作休整再出发。还有——</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒心头一震，脑海中闪过苏格兰岛事件的记忆碎片。云叶枫看漠寒在发愣，关心地问是否有哪里不适。漠寒只是摇了摇头。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>三人到飞行器仓库换上轻便宇航服，检查气密性后，云叶枫按下出舱按钮。一道蓝色屏障扫过他们，隔绝了声音。漠寒回头，见屏障停在仓库的后方。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明飞过来，递过置换枪。云叶枫接过枪，把水母装入容器，松开钳子。水母迅速反应，快速挣脱。云叶枫再次用钳子去夹，被水母躲过。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我来帮你。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明拿过云叶枫手中的钳子。这时，漠寒飞了过来。叶苏明看了眼漠寒，二话不说就把钳子塞到漠寒手里。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>哈？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>你来，毕竟你刚入队嘛，我和云叶枫磨合地差不多了。（搓手）你们两磨合一下。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒看了眼云叶枫，云叶枫微笑着点点头，带着漠寒去找另外一些水母。奇怪的是，所有水母开始对钳子有闪避行为。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>它们灵活地像无形的风，怎么抓也抓不住。要么掠过钳头，要么窜出容器，要么一开始就躲得远远的……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>要不我来？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫和漠寒交换工具。令云叶枫遗憾的是，他也抓不了一只。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒摇摇头，再次和云叶枫交换工具。一只水母游过漠寒的右肩膀，漠寒快速伸手，手中出现青蓝色粒子。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>水母好似被吸附一般固定在漠寒的掌心下，为了保证安全，漠寒可以让水母和手掌隔开了点距离。于是，水母如婴儿般被放入了容器中。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>没等水母反应，云叶枫按下按钮。突然，水母剧烈挣扎，展现出攻击行为，撞得容器晃动。云叶枫手一抖——多半是被水母撞的。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>几秒后，水母平静下来，仿佛什么都没发生。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明飞了过来，手上抱着刚从飞行器中拿出的另外几个容器。云叶枫将置换枪中的容器卸下，容器被自动封口。重复操作后，三人共捕获八只水母。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明意犹未尽。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>做得很好。现在带回样本。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫本想通过手套瞬移到他们身边，却发现电量与元钛储备莫名耗尽——明明下船前检查过。他用力掰扯触手，却纹丝不动；再看太空服数据，元钛隔膜耐久与电力都在流失——云叶枫怀疑是这大只水母干的，这水母似乎突破了投影区规则限制。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>耳机里只传来“视觉”二字，叶苏明一脸茫然，漠寒的耳朵却在毫秒内竖起，背后沁出冷汗。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>因水母轨迹难测，二人不敢用武器，怕误伤云叶枫。终于追上，云叶枫伸手，漠寒尝试抓住时却脱了手。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>大水母游至投影区边缘，渐渐消失。漠寒返程时，见一群小水母游向爆炸点，心中有了猜测。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>可我们捕获时，他们在元钛场里异常躁动。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>说完，云叶枫启动自动驾驶</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明，帮我盯着外面——我现在好困……不知道为什么……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒也困，他知道困的原因——虚空场强下元核使用元钛的量比在正常情况下多。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒不自觉地把眼睛眯上。叶苏明扫视两人，从后座爬到副驾驶，安静地盯着前方和表盘数据。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>偶然发现一只浮在空中的小土狗，脖子戴黑项圈，项圈上写着“混合意识流实验体-1”，脚穿白“鞋”，飞行自如，显然训练有素。小狗见人便摇尾巴，像个螺旋桨。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫见漠寒过来，把手机稍挪向漠寒</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>就想让她也看看世界。我看到的美好，她也该看看。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒没说话，轻轻拍了拍他的肩，转身飞向叶苏明——他看见云叶枫眼眶微红，许是需要独处。云叶枫望着他的背影，神色忧郁。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>不是，（皱眉）你想摸我头？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>都这么大了，感觉你一点没变。摸吧摸吧。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明试探着把手放在漠寒头上，轻轻抚过。漠寒眯着眼睛，有些无聊。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait &gt;&gt; 4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒惬意地看向窗外。地面景物逐渐缩小，只剩一片蓝天与大地。天色渐暗时，一颗流星划过，留下轨迹，三人不约而同望向窗外。叶苏明看得入神，甚至压在漠寒身上，一手扶窗，紧盯着外面。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>太空水母/漠寒看窗外</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音乐/落日余晖</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait &gt;&gt; 2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>（愣）不是？你也来？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音效/对讲机噪声</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;抵磁器已就绪——</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;磁力推进器已就绪——</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;三！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;二！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;一瞬间，飞行器如弹弓射出的石子般蹿出。三人顿时感受到强烈的超重感。叶苏明本想说什么，却被推力噎住，只发出一声“唔”。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;——</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;弹簧引擎成功将飞行器抛出！加速度 4.1g……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音乐/The Dragon Fell in Love with The Knight</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫看向窗外，飞行器开始减速。几分钟后，飞船靠近空间站。透过玻璃可见过道内的绿植。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>解锁档案 &gt;&gt; 投影区</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>解锁档案 &gt;&gt; 瑞州</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>解锁档案 &gt;&gt; 瑞州虚空</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>这是样本空间投影点置换枪，自带元钛，可在容器中制造强元钛场，方便你们取样。另外，工作人员刚在你们的飞行器中放了额外的取样容器，尽量多抓点。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>这是放大元核效应或引导元核的装置，由&lt;link=profile:[*]元钛&gt;元钛&lt;/link&gt;驱动，仅元核使用者可佩戴使用。唯独云叶枫的手套特殊，有纹路似的线路贴合到皮肤表面。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒！看见&lt;link=profile:[*]瑞州 | [*]兽人&gt;瑞州&lt;/link&gt;了吗？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>这次任务应较安全，不必紧张。任务点的‘水母’实际是其他空间的投影——那片区域是‘被&lt;link=profile:[*]投影区&gt;空间投影区&lt;/link&gt;’——需要解释么？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>世界之外？虚空？我只去过几次&lt;link=profile:[*]瑞州虚空&gt;瑞州虚空&lt;/link&gt;。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音效/早晨白噪音|音乐/When The Wind Blows</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音乐/Airport Lounge</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音乐/Organic Meditations Three</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音乐/Half Mystery</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>界面抖动</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒，你说为什么同一座城市，隔了一条河样子就完全不一样啊？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>因为我们现在在郊区。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>不止这一点吧？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>为了优化空气质量，政府在火灵这座城市中建造了不少小型或大型绿化区。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>原来是这样……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明听着鸟语，深吸一口气，空气中有着淡淡花香。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫说着，不经意间流露出自豪的神情。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>在我小时候……我经常看见雾霾。但现在没有了。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫远眺，脸上勾出一抹笑。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音效/对讲机打开</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>noti &gt;&gt; 已进入近地轨道 &gt;&gt; C-750 &gt;&gt; 3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1369,13 +1357,6 @@
       <sz val="9"/>
       <name val="等线"/>
       <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1433,7 +1414,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1793,2461 +1774,2461 @@
   <sheetData>
     <row r="1" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>313</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>314</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2</v>
+        <v>315</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>3</v>
+        <v>316</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>4</v>
+        <v>317</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>5</v>
+        <v>318</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>6</v>
+        <v>319</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>7</v>
+        <v>320</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
+        <v>321</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>9</v>
+        <v>322</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>10</v>
+        <v>323</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>11</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="C2" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="D2" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="E2" t="s">
         <v>182</v>
       </c>
-      <c r="E2" t="s">
-        <v>194</v>
-      </c>
       <c r="F2" s="6" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
       <c r="L2" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="D3" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="F3" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="D9" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="F9" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="D14" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="F15" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="C17" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="D17" t="s">
+        <v>170</v>
+      </c>
+      <c r="E17" t="s">
         <v>182</v>
       </c>
-      <c r="E17" t="s">
-        <v>194</v>
-      </c>
       <c r="F17" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="L17" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="D18" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="E18" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="F18" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" t="s">
         <v>17</v>
-      </c>
-      <c r="B22" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B32" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B36" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B37" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B38" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B39" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B40" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B41" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B43" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B44" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="D44" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="E44" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B45" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="D45" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="E45" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="F45" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B46" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="D46" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="F46" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B47" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B48" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B49" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B50" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B51" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C51" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="D51" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B52" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="D52" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="F52" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B53" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C53" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B54" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B55" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B56" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="D56" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B57" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="C57" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="D57" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="F57" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B58" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B59" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="C59" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B60" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B61" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="C61" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B62" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="C62" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B63" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B64" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="C64" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B65" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B66" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B67" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="D67" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="E67" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="C68" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="D68" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="E68" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="F68" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="L68" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B69" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B70" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B71" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B72" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="D72" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="E72" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="D73" t="s">
+        <v>275</v>
+      </c>
+      <c r="E73" t="s">
         <v>287</v>
       </c>
-      <c r="E73" t="s">
-        <v>299</v>
-      </c>
       <c r="F73" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B74" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B75" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B76" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B77" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B78" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B79" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B80" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B81" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B82" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B83" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="L83" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B84" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B85" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B86" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B87" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B88" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B89" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B90" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B91" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B92" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B93" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B94" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B95" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B96" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B97" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B98" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B99" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B100" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B101" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B102" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B103" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B104" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B105" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B106" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B107" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B108" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B109" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B110" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="D110" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B111" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D111" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="F111" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B112" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B113" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B114" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D114" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="D115" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="F115" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B116" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="D116" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F116" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B117" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="D117" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="E117" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="F117" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B118" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="C118" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="E118" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="F118" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B119" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="C119" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B120" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C120" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B121" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C121" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B122" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B123" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D123" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B124" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C124" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="D124" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="F124" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B125" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B126" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="D126" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B127" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C127" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="D127" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="F127" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B128" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B129" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D129" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A130" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B130" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="C130" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="D130" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="F130" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A131" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B131" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A132" s="3" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="B132" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A133" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B133" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A134" s="3" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="B134" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="L134" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A135" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B135" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A136" s="3" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="B136" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A137" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B137" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A138" s="3" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="B138" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A139" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B139" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="B140" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="D140" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A141" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B141" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B142" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="C142" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="D142" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="F142" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A143" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B143" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="D143" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F143" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A144" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B144" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A145" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B145" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A146" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B146" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="L146" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A147" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B147" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A148" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B148" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A149" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B149" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A150" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B150" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="D150" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A151" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B151" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="D151" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="F151" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B152" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="D152" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="F152" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B153" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A154" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B154" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A155" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B155" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A156" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B156" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A157" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B157" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A158" s="3" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="B158" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="H158" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A159" s="3" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="B159" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="H159" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A160" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B160" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="H160" s="3"/>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161" s="3" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="B161" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B162" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="H162" s="3"/>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163" s="3" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="B163" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B164" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="H164" s="3"/>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165" s="3" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="B165" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="H165" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166" s="3" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B166" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A167" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B167" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="H167" s="3"/>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B168" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="H168" s="3"/>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A169" s="3" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="B169" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="H169" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A170" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B170" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="H170" s="3"/>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B171" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="H171" s="3"/>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B172" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H172" s="3"/>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B173" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="H173" s="3"/>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A174" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B174" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="H174" s="3"/>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A175" s="3" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="B175" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="H175" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A176" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B176" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="H176" s="3"/>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A177" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B177" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="H177" s="3"/>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A178" s="3" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="B178" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A179" s="3" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="B179" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="H179" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A180" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B180" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H180" s="3"/>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A181" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B181" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="H181" s="3"/>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A182" s="3" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="B182" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="D182" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="E182" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="H182" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A183" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B183" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="D183" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="E183" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="F183" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="H183" s="3"/>
       <c r="L183" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A184" s="3" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="B184" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A185" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B185" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="H185" s="3"/>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B186" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="H186" s="3"/>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B187" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="H187" s="3"/>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A188" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B188" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="H188" s="3"/>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A189" s="3" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="B189" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="H189" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A190" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B190" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="H190" s="3"/>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A191" s="3" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B191" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="H191" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A192" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B192" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B193" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B194" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="L194" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B195" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B196" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A197" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B197" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A198" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B198" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A199" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B199" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A200" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B200" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A201" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B201" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="D201" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="F201" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A202" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B202" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="D202" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F202" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A203" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B203" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="D203" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A204" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B204" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="D204" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="E204" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="F204" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A205" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B205" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="E205" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A206" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B206" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A207" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B207" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A208" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B208" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A209" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B209" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A210" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B210" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A211" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B211" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A212" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B212" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A213" s="3" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="B213" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A214" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B214" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A215" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B215" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A216" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B216" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A217" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B217" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A218" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B218" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A219" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B219" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A220" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B220" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A221" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B221" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A222" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B222" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A223" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B223" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A224" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B224" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A225" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B225" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B226" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="D226" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="E226" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B227" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="D227" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="E227" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="F227" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B228" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B229" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A230" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B230" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A231" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B231" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A232" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B232" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A233" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B233" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B234" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B235" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A236" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B236" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A237" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B237" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A238" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B238" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A239" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B239" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A240" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B240" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A241" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B241" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
     </row>
     <row r="242" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A242" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B242" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
     </row>
     <row r="243" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A243" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B243" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A244" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B244" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A245" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B245" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A246" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B246" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="247" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A247" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B247" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A248" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B248" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
     </row>
     <row r="249" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A249" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B249" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A250" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B250" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A251" s="3" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="B251" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="C251" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="L251" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A252" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B252" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A253" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B253" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A254" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B254" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A255" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B255" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A256" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B256" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A257" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B257" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A258" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B258" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B259" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B260" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="D260" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B261" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="D261" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A262" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B262" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.2">
       <c r="L263" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Chapter/Chapter2.xlsx
+++ b/Assets/StreamingAssets/Chapter/Chapter2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\shina\Assets\StreamingAssets\Chapter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122E3B28-988D-4D19-9E78-32A3C791374E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69FF8545-E163-4F6D-A516-1181E33D37CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15390" xr2:uid="{93CEB1B2-C3AD-4226-8194-AA135A927779}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{93CEB1B2-C3AD-4226-8194-AA135A927779}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,6 +38,54 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="325">
   <si>
+    <t>人物</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>对话</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>语音</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>背景/cg</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>背景音乐</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>转场特效</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>立绘</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>对话框头像</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>#TAG</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>选项</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>QTE</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>指令</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>云叶枫有太空经验，漠寒队员，听说你也有相关履历——</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1286,49 +1334,13 @@
   <si>
     <t>noti &gt;&gt; 已进入近地轨道 &gt;&gt; C-750 &gt;&gt; 3</t>
     <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>人物</t>
-  </si>
-  <si>
-    <t>对话</t>
-  </si>
-  <si>
-    <t>语音</t>
-  </si>
-  <si>
-    <t>背景/cg</t>
-  </si>
-  <si>
-    <t>背景音乐</t>
-  </si>
-  <si>
-    <t>转场特效</t>
-  </si>
-  <si>
-    <t>立绘层</t>
-  </si>
-  <si>
-    <t>对话框头像</t>
-  </si>
-  <si>
-    <t>#TAG</t>
-  </si>
-  <si>
-    <t>选项</t>
-  </si>
-  <si>
-    <t>TE. HUD层</t>
-  </si>
-  <si>
-    <t>指令</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1357,6 +1369,13 @@
       <sz val="9"/>
       <name val="等线"/>
       <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1414,7 +1433,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1774,2461 +1793,2461 @@
   <sheetData>
     <row r="1" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>313</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>314</v>
+        <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>315</v>
+        <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>316</v>
+        <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>317</v>
+        <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>318</v>
+        <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>319</v>
+        <v>6</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>320</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>321</v>
+        <v>8</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>322</v>
+        <v>9</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>323</v>
+        <v>10</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>324</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="C2" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="E2" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
       <c r="L2" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="D3" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="F3" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="D9" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="F9" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="D14" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="F15" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="C17" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="D17" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="E17" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="F17" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="L17" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="D18" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="E18" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="F18" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B27" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B28" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B30" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B31" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B33" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B35" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B36" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B38" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B39" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B40" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B41" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B42" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B43" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B44" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="D44" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="E44" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B45" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="D45" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="E45" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="F45" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B46" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="D46" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="F46" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B47" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B48" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B49" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B50" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B51" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="C51" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="D51" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B52" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="D52" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="F52" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B53" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C53" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B54" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B55" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B56" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D56" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B57" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="C57" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="D57" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="F57" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B58" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B59" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="C59" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B60" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B61" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="C61" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B62" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="C62" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B63" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B64" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="C64" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B65" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B66" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B67" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="D67" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="E67" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="C68" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="D68" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="E68" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="F68" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="L68" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B69" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B70" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B71" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B72" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="D72" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="E72" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="D73" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="E73" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="F73" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B74" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B75" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B76" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B77" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B78" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B79" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B80" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B81" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B82" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B83" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="L83" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B84" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B85" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B86" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B87" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B88" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B89" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B90" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B91" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B92" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B93" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B94" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B95" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B96" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B97" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B98" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B99" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B100" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B101" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B102" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B103" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B104" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B105" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B106" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B107" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B108" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B109" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B110" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="D110" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B111" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D111" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="F111" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B112" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B113" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B114" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="D114" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="D115" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="F115" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B116" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="D116" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="F116" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B117" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="D117" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="E117" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="F117" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B118" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="C118" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="E118" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="F118" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B119" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="C119" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B120" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C120" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B121" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C121" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B122" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B123" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="D123" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B124" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C124" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="D124" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="F124" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B125" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B126" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D126" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B127" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C127" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="D127" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="F127" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B128" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B129" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="D129" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A130" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B130" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="C130" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="D130" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="F130" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A131" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B131" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A132" s="3" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="B132" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A133" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B133" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A134" s="3" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="B134" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="L134" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A135" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B135" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A136" s="3" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="B136" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A137" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B137" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A138" s="3" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="B138" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A139" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B139" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="B140" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="D140" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A141" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B141" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B142" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C142" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="D142" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="F142" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A143" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B143" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="D143" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="F143" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A144" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B144" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A145" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B145" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A146" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B146" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="L146" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A147" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B147" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A148" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B148" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A149" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B149" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A150" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B150" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="D150" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A151" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B151" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="D151" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="F151" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B152" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="D152" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="F152" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B153" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A154" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B154" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A155" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B155" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A156" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B156" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A157" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B157" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A158" s="3" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="B158" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="H158" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A159" s="3" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="B159" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="H159" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A160" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B160" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="H160" s="3"/>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161" s="3" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="B161" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B162" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="H162" s="3"/>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163" s="3" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="B163" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B164" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="H164" s="3"/>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165" s="3" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="B165" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="H165" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166" s="3" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="B166" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A167" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B167" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="H167" s="3"/>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B168" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="H168" s="3"/>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A169" s="3" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="B169" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="H169" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A170" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B170" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="H170" s="3"/>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B171" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="H171" s="3"/>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B172" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="H172" s="3"/>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B173" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="H173" s="3"/>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A174" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B174" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="H174" s="3"/>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A175" s="3" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="B175" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="H175" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A176" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B176" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="H176" s="3"/>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A177" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B177" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="H177" s="3"/>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A178" s="3" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="B178" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A179" s="3" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="B179" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="H179" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A180" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B180" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="H180" s="3"/>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A181" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B181" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="H181" s="3"/>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A182" s="3" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="B182" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="D182" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="E182" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="H182" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A183" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B183" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D183" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="E183" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="F183" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="H183" s="3"/>
       <c r="L183" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A184" s="3" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="B184" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A185" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B185" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="H185" s="3"/>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B186" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="H186" s="3"/>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B187" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="H187" s="3"/>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A188" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B188" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="H188" s="3"/>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A189" s="3" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="B189" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="H189" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A190" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B190" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="H190" s="3"/>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A191" s="3" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="B191" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="H191" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A192" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B192" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B193" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B194" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="L194" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B195" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B196" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A197" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B197" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A198" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B198" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A199" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B199" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A200" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B200" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A201" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B201" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="D201" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="F201" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A202" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B202" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="D202" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="F202" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A203" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B203" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="D203" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A204" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B204" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="D204" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="E204" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="F204" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A205" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B205" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="E205" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A206" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B206" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A207" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B207" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A208" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B208" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A209" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B209" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A210" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B210" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A211" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B211" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A212" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B212" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A213" s="3" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="B213" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A214" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B214" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A215" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B215" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A216" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B216" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A217" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B217" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A218" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B218" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A219" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B219" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A220" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B220" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A221" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B221" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A222" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B222" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A223" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B223" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A224" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B224" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A225" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B225" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B226" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="D226" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="E226" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B227" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="D227" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="E227" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="F227" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B228" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B229" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A230" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B230" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A231" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B231" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A232" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B232" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A233" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B233" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B234" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B235" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A236" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B236" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A237" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B237" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A238" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B238" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A239" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B239" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A240" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B240" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A241" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B241" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
     </row>
     <row r="242" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A242" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B242" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
     </row>
     <row r="243" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A243" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B243" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A244" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B244" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A245" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B245" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A246" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B246" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
     </row>
     <row r="247" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A247" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B247" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A248" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B248" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="249" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A249" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B249" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A250" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B250" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A251" s="3" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="B251" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="C251" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="L251" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A252" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B252" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A253" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B253" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A254" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B254" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A255" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B255" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A256" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B256" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A257" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B257" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A258" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B258" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B259" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B260" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="D260" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B261" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="D261" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A262" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B262" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.2">
       <c r="L263" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Chapter/Chapter2.xlsx
+++ b/Assets/StreamingAssets/Chapter/Chapter2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\shina\Assets\StreamingAssets\Chapter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69FF8545-E163-4F6D-A516-1181E33D37CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F360E70-83EB-4A07-AD49-822CB7EA853F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{93CEB1B2-C3AD-4226-8194-AA135A927779}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15390" xr2:uid="{93CEB1B2-C3AD-4226-8194-AA135A927779}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="328">
   <si>
     <t>人物</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -213,10 +213,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>漠寒，我有点紧张。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>我怎么看不出来？</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -288,10 +284,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>——你们多久没回家了？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>不像你能天天回。我也有两三个月了——队长，还不开车？</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -556,30 +548,10 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>三人有惊无险回到飞行器后舱，舱门关闭，蓝色屏障扫过停在门口。叶苏明和云叶枫脱去宇航服，云叶枫返回驾驶位时，漠寒却再次向外走去。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>漠寒？</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>叶苏明拉住他，凝视着他的眼睛。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我去求证件事，马上回来。（拨开手）我不会有事。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>果然……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒求证完毕，返回舱内。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>我感觉我像是死了一次。吓出心脏病了。</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -624,30 +596,10 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>置换时，它受到了本地虚空场影响，所以躁动。后来安静，是因为太空服的元钛隔膜覆盖了它——对了，介意明天我教你用元核吗？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>元核？怎么说？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我看到你用了元核。那团橙色的光。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>你说那个爆炸？真是元核弄的？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>是啊！我用元核几百年了，还能看不出来？</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>（小声）原来不是手套突然管用了……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>返回太空站，将水母交给中央实验室的龙人后，三人向周文涵申请逗留，获允后直奔太空花园。先合影留念，再各自闲逛。因时间充裕，他们见到了反重力喷泉、人工小湖……</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -668,10 +620,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>漠寒常想这些，此刻却有了答案——为了存在而存在。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>叶苏明不知何时凑过来</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -932,18 +880,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>叶苏明缓缓松开，在窗边静静注视。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒飞向附近的水母群，手上聚集元钛，散出蓝色微粒。水母如饿狼般涌向他的手，似在舔舐什么一样。他移动手，水母也随之跟上。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>太空水母/太空水母3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>音效/拍照1</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1008,10 +944,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>因为漠寒太吸引我了。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>舱内一时寂静，漠寒与云叶枫仿佛“死机”。突然，云叶枫大笑，一言不发，好奇漠寒会说些什么。</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1124,18 +1056,10 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>大水母游至投影区边缘，渐渐消失。漠寒返程时，见一群小水母游向爆炸点，心中有了猜测。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>可我们捕获时，他们在元钛场里异常躁动。</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>说完，云叶枫启动自动驾驶</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>叶苏明，帮我盯着外面——我现在好困……不知道为什么……</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1144,10 +1068,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>漠寒不自觉地把眼睛眯上。叶苏明扫视两人，从后座爬到副驾驶，安静地盯着前方和表盘数据。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>偶然发现一只浮在空中的小土狗，脖子戴黑项圈，项圈上写着“混合意识流实验体-1”，脚穿白“鞋”，飞行自如，显然训练有素。小狗见人便摇尾巴，像个螺旋桨。</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1260,10 +1180,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>漠寒！看见&lt;link=profile:[*]瑞州 | [*]兽人&gt;瑞州&lt;/link&gt;了吗？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>这次任务应较安全，不必紧张。任务点的‘水母’实际是其他空间的投影——那片区域是‘被&lt;link=profile:[*]投影区&gt;空间投影区&lt;/link&gt;’——需要解释么？</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1333,6 +1249,102 @@
   </si>
   <si>
     <t>noti &gt;&gt; 已进入近地轨道 &gt;&gt; C-750 &gt;&gt; 3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>老大，我有点紧张。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶苏明似乎很喜欢叫你‘老大’？漠寒，为什么？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>老大！看见&lt;link=profile:[*]瑞州 | [*]兽人&gt;瑞州&lt;/link&gt;了吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>啊，他就是一直这么叫我的。我也不知道为什么，从什么时候开始。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>因为漠寒很适合当头狼！在漠寒旁边很有安全感！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>头狼……你们多久没回家了？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>因为老大你太吸引我了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>大水母游至投影区边缘，渐渐消失。漠寒返程时，见一群小水母游向爆炸点，心中突然好奇起来，感觉发现了什么特性。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>三人有惊无险回到飞行器后舱，舱门关闭，蓝色屏障扫过停在门口。叶苏明和云叶枫脱去宇航服，漠寒却拿起装着水母的容器摆弄起来。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒手上聚集元钛，散出蓝色微粒。水母如饿狼般涌向他的手，一次一次撞在容器内壁上。他移动手，水母也随之跟上。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>也许……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶苏明好奇地看着漠寒。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒感觉求证得差不多了，为了严谨，他想出舱门试试那些“野生型”水母，想到刚才云叶枫的遭遇，漠寒还是选择脱下了宇航服。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>返回座位的漠寒和云叶枫满脸劳累。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>置换时，它受到了本地虚空场影响，所以躁动。后来安静，是因为太空服的元钛隔膜覆盖了它。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞行器中的三人安静下来，叶苏明见云叶枫长时间不说话，于是夸赞道：</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>说真的，队长。你搞出的那个黄色的爆炸真的超级牛逼的！——为什么不早点使出来？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我使出来的？我？难道不是漠寒？我的手套在那时突然坏了！你说那个爆炸？真是我弄的？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>怪不得你等我们去救——我知道了，云叶枫，介意我明天教你使用元核吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫先是怀疑自己是否真的能做到脱离辅助装备较好地使用元核，但再次想到那个爆炸，便好奇并愉快地答应下来了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒不自觉地把眼睛眯上。叶苏明扫视两人，从后座爬到副驾驶，启动自动寻路，安静地盯着前方和表盘数据。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒突然回忆起来，小时候他经常追问父母“既然爸爸妈妈你们不喜欢上班，为什么不当个和尚呢？”“世界上有这么多无意义的事情，为什么人要去做呢？”“人最后会死去，活着的意义是什么呢？”他的父母经常会温柔地回答“这需要你自己去寻找答案……”</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>每个人都走在自己的路上，赋予自己的意义，唯心，成为自己。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>老大？</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1782,7 +1794,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3CF46EA-649E-46D2-A2F1-55ADFE170F2E}">
-  <dimension ref="A1:L263"/>
+  <dimension ref="A1:L266"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.25" style="3" customWidth="1"/>
@@ -1834,24 +1846,24 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E2" t="s">
         <v>181</v>
       </c>
-      <c r="C2" t="s">
-        <v>183</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="E2" t="s">
-        <v>194</v>
-      </c>
       <c r="F2" s="6" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
       <c r="L2" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -1859,13 +1871,13 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="D3" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="F3" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
@@ -1897,7 +1909,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
@@ -1908,7 +1920,7 @@
         <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -1916,13 +1928,13 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="D9" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="F9" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
@@ -1962,10 +1974,10 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="D14" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
@@ -1973,15 +1985,15 @@
         <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="F15" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
@@ -1989,36 +2001,36 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="C17" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="D17" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="E17" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="F17" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="L17" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="D18" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="E18" t="s">
-        <v>309</v>
+        <v>288</v>
       </c>
       <c r="F18" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
@@ -2066,7 +2078,7 @@
         <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
@@ -2090,7 +2102,7 @@
         <v>22</v>
       </c>
       <c r="B27" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
@@ -2098,7 +2110,7 @@
         <v>20</v>
       </c>
       <c r="B28" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
@@ -2122,7 +2134,7 @@
         <v>20</v>
       </c>
       <c r="B31" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
@@ -2130,7 +2142,7 @@
         <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
@@ -2138,7 +2150,7 @@
         <v>20</v>
       </c>
       <c r="B33" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
@@ -2146,7 +2158,7 @@
         <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
@@ -2154,7 +2166,7 @@
         <v>14</v>
       </c>
       <c r="B35" t="s">
-        <v>319</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
@@ -2162,7 +2174,7 @@
         <v>22</v>
       </c>
       <c r="B36" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
@@ -2170,7 +2182,7 @@
         <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
@@ -2178,7 +2190,7 @@
         <v>20</v>
       </c>
       <c r="B38" t="s">
-        <v>316</v>
+        <v>295</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
@@ -2186,7 +2198,7 @@
         <v>14</v>
       </c>
       <c r="B39" t="s">
-        <v>320</v>
+        <v>299</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
@@ -2194,7 +2206,7 @@
         <v>17</v>
       </c>
       <c r="B40" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
@@ -2202,7 +2214,7 @@
         <v>20</v>
       </c>
       <c r="B41" t="s">
-        <v>317</v>
+        <v>296</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
@@ -2210,7 +2222,7 @@
         <v>20</v>
       </c>
       <c r="B42" t="s">
-        <v>321</v>
+        <v>300</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
@@ -2218,7 +2230,7 @@
         <v>14</v>
       </c>
       <c r="B43" t="s">
-        <v>322</v>
+        <v>301</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
@@ -2226,13 +2238,13 @@
         <v>22</v>
       </c>
       <c r="B44" t="s">
-        <v>318</v>
+        <v>297</v>
       </c>
       <c r="D44" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="E44" t="s">
-        <v>309</v>
+        <v>288</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
@@ -2240,16 +2252,16 @@
         <v>14</v>
       </c>
       <c r="B45" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="D45" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="E45" t="s">
-        <v>310</v>
+        <v>289</v>
       </c>
       <c r="F45" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
@@ -2257,13 +2269,13 @@
         <v>14</v>
       </c>
       <c r="B46" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="D46" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="F46" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
@@ -2306,10 +2318,10 @@
         <v>39</v>
       </c>
       <c r="C51" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="D51" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
@@ -2320,10 +2332,10 @@
         <v>41</v>
       </c>
       <c r="D52" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="F52" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
@@ -2334,7 +2346,7 @@
         <v>43</v>
       </c>
       <c r="C53" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
@@ -2342,7 +2354,7 @@
         <v>22</v>
       </c>
       <c r="B54" t="s">
-        <v>44</v>
+        <v>304</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
@@ -2350,7 +2362,7 @@
         <v>14</v>
       </c>
       <c r="B55" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
@@ -2358,27 +2370,27 @@
         <v>17</v>
       </c>
       <c r="B56" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D56" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B57" t="s">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="C57" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="D57" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="F57" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
@@ -2386,18 +2398,18 @@
         <v>20</v>
       </c>
       <c r="B58" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B59" t="s">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="C59" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
@@ -2405,29 +2417,29 @@
         <v>22</v>
       </c>
       <c r="B60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B61" t="s">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="C61" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B62" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="C62" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
@@ -2435,15 +2447,15 @@
         <v>14</v>
       </c>
       <c r="B63" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B64" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="C64" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
@@ -2451,15 +2463,15 @@
         <v>14</v>
       </c>
       <c r="B65" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B66" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
@@ -2467,33 +2479,33 @@
         <v>14</v>
       </c>
       <c r="B67" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="D67" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="E67" t="s">
-        <v>310</v>
+        <v>289</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="C68" t="s">
-        <v>323</v>
+        <v>302</v>
       </c>
       <c r="D68" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="E68" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="F68" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="L68" t="s">
-        <v>324</v>
+        <v>303</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
@@ -2501,7 +2513,7 @@
         <v>14</v>
       </c>
       <c r="B69" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
@@ -2509,7 +2521,7 @@
         <v>22</v>
       </c>
       <c r="B70" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
@@ -2517,7 +2529,7 @@
         <v>20</v>
       </c>
       <c r="B71" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.2">
@@ -2525,27 +2537,27 @@
         <v>22</v>
       </c>
       <c r="B72" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="D72" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="E72" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="D73" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="E73" t="s">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="F73" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.2">
@@ -2553,7 +2565,7 @@
         <v>14</v>
       </c>
       <c r="B74" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
@@ -2561,7 +2573,7 @@
         <v>17</v>
       </c>
       <c r="B75" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
@@ -2569,7 +2581,7 @@
         <v>20</v>
       </c>
       <c r="B76" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
@@ -2577,7 +2589,7 @@
         <v>22</v>
       </c>
       <c r="B77" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.2">
@@ -2585,7 +2597,7 @@
         <v>20</v>
       </c>
       <c r="B78" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
@@ -2593,7 +2605,7 @@
         <v>14</v>
       </c>
       <c r="B79" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
@@ -2601,7 +2613,7 @@
         <v>22</v>
       </c>
       <c r="B80" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.2">
@@ -2609,7 +2621,7 @@
         <v>20</v>
       </c>
       <c r="B81" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.2">
@@ -2617,7 +2629,7 @@
         <v>14</v>
       </c>
       <c r="B82" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.2">
@@ -2628,7 +2640,7 @@
         <v>306</v>
       </c>
       <c r="L83" t="s">
-        <v>302</v>
+        <v>282</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.2">
@@ -2636,7 +2648,7 @@
         <v>14</v>
       </c>
       <c r="B84" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.2">
@@ -2644,7 +2656,7 @@
         <v>22</v>
       </c>
       <c r="B85" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.2">
@@ -2652,7 +2664,7 @@
         <v>17</v>
       </c>
       <c r="B86" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.2">
@@ -2660,7 +2672,7 @@
         <v>22</v>
       </c>
       <c r="B87" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.2">
@@ -2668,7 +2680,7 @@
         <v>20</v>
       </c>
       <c r="B88" t="s">
-        <v>63</v>
+        <v>305</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.2">
@@ -2676,7 +2688,7 @@
         <v>17</v>
       </c>
       <c r="B89" t="s">
-        <v>62</v>
+        <v>307</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.2">
@@ -2684,7 +2696,7 @@
         <v>22</v>
       </c>
       <c r="B90" t="s">
-        <v>64</v>
+        <v>308</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.2">
@@ -2692,7 +2704,7 @@
         <v>20</v>
       </c>
       <c r="B91" t="s">
-        <v>65</v>
+        <v>309</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.2">
@@ -2700,31 +2712,31 @@
         <v>17</v>
       </c>
       <c r="B92" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B93" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B94" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B95" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.2">
@@ -2732,152 +2744,146 @@
         <v>20</v>
       </c>
       <c r="B96" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A97" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B97" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A98" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B98" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A99" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B99" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A100" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B100" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B101" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A97" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B97" t="s">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A102" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B102" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A98" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B98" t="s">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A103" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B103" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A99" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B99" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A100" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B100" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A101" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B101" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A102" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B102" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A103" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B103" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B104" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B105" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B106" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A107" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B106" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A107" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="B107" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B108" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A109" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B108" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A109" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="B109" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B110" t="s">
-        <v>245</v>
-      </c>
-      <c r="D110" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A111" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B111" t="s">
-        <v>80</v>
-      </c>
-      <c r="D111" t="s">
-        <v>207</v>
-      </c>
-      <c r="F111" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A112" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B112" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B113" t="s">
-        <v>247</v>
+        <v>228</v>
+      </c>
+      <c r="D113" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
@@ -2885,21 +2891,21 @@
         <v>22</v>
       </c>
       <c r="B114" t="s">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="D114" t="s">
-        <v>207</v>
+        <v>194</v>
+      </c>
+      <c r="F114" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D115" t="s">
-        <v>208</v>
-      </c>
-      <c r="F115" t="s">
-        <v>190</v>
+        <v>17</v>
+      </c>
+      <c r="B115" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
@@ -2907,156 +2913,150 @@
         <v>14</v>
       </c>
       <c r="B116" t="s">
-        <v>300</v>
-      </c>
-      <c r="D116" t="s">
-        <v>210</v>
-      </c>
-      <c r="F116" t="s">
-        <v>186</v>
+        <v>230</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A117" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="B117" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="D117" t="s">
-        <v>215</v>
-      </c>
-      <c r="E117" t="s">
-        <v>299</v>
-      </c>
-      <c r="F117" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B118" t="s">
-        <v>204</v>
-      </c>
-      <c r="C118" t="s">
-        <v>211</v>
-      </c>
-      <c r="E118" t="s">
-        <v>311</v>
+        <v>180</v>
+      </c>
+      <c r="D118" t="s">
+        <v>195</v>
       </c>
       <c r="F118" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="B119" t="s">
-        <v>81</v>
-      </c>
-      <c r="C119" t="s">
-        <v>291</v>
+        <v>280</v>
+      </c>
+      <c r="D119" t="s">
+        <v>197</v>
+      </c>
+      <c r="F119" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A120" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="B120" t="s">
-        <v>82</v>
-      </c>
-      <c r="C120" t="s">
-        <v>200</v>
+        <v>196</v>
+      </c>
+      <c r="D120" t="s">
+        <v>202</v>
+      </c>
+      <c r="E120" t="s">
+        <v>279</v>
+      </c>
+      <c r="F120" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B121" t="s">
-        <v>83</v>
+        <v>191</v>
       </c>
       <c r="C121" t="s">
-        <v>212</v>
+        <v>198</v>
+      </c>
+      <c r="E121" t="s">
+        <v>290</v>
+      </c>
+      <c r="F121" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="B122" t="s">
-        <v>213</v>
+        <v>79</v>
+      </c>
+      <c r="C122" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A123" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="B123" t="s">
-        <v>214</v>
-      </c>
-      <c r="D123" t="s">
-        <v>215</v>
+        <v>80</v>
+      </c>
+      <c r="C123" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A124" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="B124" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C124" t="s">
-        <v>217</v>
-      </c>
-      <c r="D124" t="s">
-        <v>216</v>
-      </c>
-      <c r="F124" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A125" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="B125" t="s">
-        <v>85</v>
+        <v>200</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B126" t="s">
-        <v>86</v>
+        <v>201</v>
       </c>
       <c r="D126" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A127" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="B127" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C127" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D127" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="F127" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A128" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="B128" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A129" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="B129" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D129" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.2">
@@ -3064,32 +3064,35 @@
         <v>14</v>
       </c>
       <c r="B130" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C130" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="D130" t="s">
-        <v>218</v>
+        <v>169</v>
       </c>
       <c r="F130" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A131" s="3" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B131" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A132" s="3" t="s">
-        <v>93</v>
+        <v>17</v>
       </c>
       <c r="B132" t="s">
-        <v>92</v>
+        <v>87</v>
+      </c>
+      <c r="D132" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.2">
@@ -3097,140 +3100,146 @@
         <v>14</v>
       </c>
       <c r="B133" t="s">
-        <v>94</v>
+        <v>88</v>
+      </c>
+      <c r="C133" t="s">
+        <v>199</v>
+      </c>
+      <c r="D133" t="s">
+        <v>205</v>
+      </c>
+      <c r="F133" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A134" s="3" t="s">
-        <v>93</v>
+        <v>14</v>
       </c>
       <c r="B134" t="s">
-        <v>307</v>
-      </c>
-      <c r="L134" t="s">
-        <v>301</v>
+        <v>89</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A135" s="3" t="s">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="B135" t="s">
-        <v>249</v>
+        <v>90</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A136" s="3" t="s">
-        <v>93</v>
+        <v>14</v>
       </c>
       <c r="B136" t="s">
-        <v>250</v>
+        <v>92</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A137" s="3" t="s">
-        <v>14</v>
+        <v>91</v>
       </c>
       <c r="B137" t="s">
-        <v>95</v>
+        <v>286</v>
+      </c>
+      <c r="L137" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A138" s="3" t="s">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="B138" t="s">
-        <v>304</v>
+        <v>232</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A139" s="3" t="s">
-        <v>14</v>
+        <v>91</v>
       </c>
       <c r="B139" t="s">
-        <v>96</v>
+        <v>233</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B140" t="s">
         <v>93</v>
-      </c>
-      <c r="B140" t="s">
-        <v>97</v>
-      </c>
-      <c r="D140" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A141" s="3" t="s">
-        <v>14</v>
+        <v>91</v>
       </c>
       <c r="B141" t="s">
-        <v>251</v>
+        <v>284</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A142" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="B142" t="s">
-        <v>219</v>
-      </c>
-      <c r="C142" t="s">
-        <v>211</v>
-      </c>
-      <c r="D142" t="s">
-        <v>215</v>
-      </c>
-      <c r="F142" t="s">
-        <v>190</v>
+        <v>94</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A143" s="3" t="s">
-        <v>14</v>
+        <v>91</v>
       </c>
       <c r="B143" t="s">
-        <v>220</v>
+        <v>95</v>
       </c>
       <c r="D143" t="s">
-        <v>210</v>
-      </c>
-      <c r="F143" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A144" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B144" t="s">
-        <v>99</v>
+        <v>234</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A145" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="B145" t="s">
-        <v>98</v>
+        <v>206</v>
+      </c>
+      <c r="C145" t="s">
+        <v>198</v>
+      </c>
+      <c r="D145" t="s">
+        <v>202</v>
+      </c>
+      <c r="F145" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A146" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B146" t="s">
-        <v>308</v>
-      </c>
-      <c r="L146" t="s">
-        <v>303</v>
+        <v>207</v>
+      </c>
+      <c r="D146" t="s">
+        <v>197</v>
+      </c>
+      <c r="F146" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A147" s="3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B147" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.2">
@@ -3238,56 +3247,53 @@
         <v>17</v>
       </c>
       <c r="B148" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A149" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B149" t="s">
-        <v>102</v>
+        <v>287</v>
+      </c>
+      <c r="L149" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A150" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B150" t="s">
-        <v>103</v>
-      </c>
-      <c r="D150" t="s">
-        <v>210</v>
+        <v>98</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A151" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B151" t="s">
-        <v>221</v>
-      </c>
-      <c r="D151" t="s">
-        <v>182</v>
-      </c>
-      <c r="F151" t="s">
-        <v>190</v>
+        <v>99</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A152" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="B152" t="s">
-        <v>104</v>
-      </c>
-      <c r="D152" t="s">
-        <v>222</v>
-      </c>
-      <c r="F152" t="s">
-        <v>190</v>
+        <v>100</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A153" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="B153" t="s">
-        <v>105</v>
+        <v>101</v>
+      </c>
+      <c r="D153" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.2">
@@ -3295,23 +3301,29 @@
         <v>14</v>
       </c>
       <c r="B154" t="s">
-        <v>106</v>
+        <v>208</v>
+      </c>
+      <c r="D154" t="s">
+        <v>169</v>
+      </c>
+      <c r="F154" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A155" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="B155" t="s">
-        <v>107</v>
+        <v>102</v>
+      </c>
+      <c r="D155" t="s">
+        <v>209</v>
+      </c>
+      <c r="F155" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A156" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="B156" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.2">
@@ -3319,29 +3331,23 @@
         <v>14</v>
       </c>
       <c r="B157" t="s">
-        <v>252</v>
+        <v>104</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A158" s="3" t="s">
-        <v>110</v>
+        <v>22</v>
       </c>
       <c r="B158" t="s">
-        <v>109</v>
-      </c>
-      <c r="H158" s="3" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A159" s="3" t="s">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="B159" t="s">
-        <v>111</v>
-      </c>
-      <c r="H159" s="3" t="s">
-        <v>20</v>
+        <v>106</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.2">
@@ -3349,70 +3355,69 @@
         <v>14</v>
       </c>
       <c r="B160" t="s">
-        <v>113</v>
-      </c>
-      <c r="H160" s="3"/>
+        <v>235</v>
+      </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B161" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162" s="3" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="B162" t="s">
-        <v>253</v>
-      </c>
-      <c r="H162" s="3"/>
+        <v>109</v>
+      </c>
+      <c r="H162" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163" s="3" t="s">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="B163" t="s">
-        <v>254</v>
-      </c>
-      <c r="H163" s="3" t="s">
-        <v>22</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="H163" s="3"/>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164" s="3" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="B164" t="s">
-        <v>255</v>
-      </c>
-      <c r="H164" s="3"/>
+        <v>112</v>
+      </c>
+      <c r="H164" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165" s="3" t="s">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="B165" t="s">
-        <v>257</v>
-      </c>
-      <c r="H165" s="3" t="s">
-        <v>22</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="H165" s="3"/>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166" s="3" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B166" t="s">
-        <v>256</v>
+        <v>237</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.2">
@@ -3420,28 +3425,30 @@
         <v>14</v>
       </c>
       <c r="B167" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="H167" s="3"/>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168" s="3" t="s">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="B168" t="s">
-        <v>259</v>
-      </c>
-      <c r="H168" s="3"/>
+        <v>240</v>
+      </c>
+      <c r="H168" s="3" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A169" s="3" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="B169" t="s">
-        <v>260</v>
+        <v>239</v>
       </c>
       <c r="H169" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.2">
@@ -3449,54 +3456,54 @@
         <v>14</v>
       </c>
       <c r="B170" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="H170" s="3"/>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A171" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="B171" t="s">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="H171" s="3"/>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A172" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="B172" t="s">
-        <v>263</v>
-      </c>
-      <c r="H172" s="3"/>
+        <v>243</v>
+      </c>
+      <c r="H172" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A173" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="B173" t="s">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="H173" s="3"/>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A174" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="B174" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="H174" s="3"/>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A175" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="B175" t="s">
-        <v>115</v>
-      </c>
-      <c r="H175" s="3" t="s">
-        <v>20</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="H175" s="3"/>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A176" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="B176" t="s">
-        <v>116</v>
+        <v>247</v>
       </c>
       <c r="H176" s="3"/>
     </row>
@@ -3505,16 +3512,16 @@
         <v>14</v>
       </c>
       <c r="B177" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="H177" s="3"/>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A178" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B178" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H178" s="3" t="s">
         <v>20</v>
@@ -3522,48 +3529,42 @@
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A179" s="3" t="s">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="B179" t="s">
-        <v>118</v>
-      </c>
-      <c r="H179" s="3" t="s">
-        <v>22</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="H179" s="3"/>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A180" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B180" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="H180" s="3"/>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A181" s="3" t="s">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="B181" t="s">
-        <v>268</v>
-      </c>
-      <c r="H181" s="3"/>
+        <v>115</v>
+      </c>
+      <c r="H181" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A182" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B182" t="s">
-        <v>119</v>
-      </c>
-      <c r="D182" t="s">
-        <v>222</v>
-      </c>
-      <c r="E182" t="s">
-        <v>311</v>
+        <v>116</v>
       </c>
       <c r="H182" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.2">
@@ -3571,169 +3572,189 @@
         <v>14</v>
       </c>
       <c r="B183" t="s">
-        <v>120</v>
-      </c>
-      <c r="D183" t="s">
-        <v>223</v>
-      </c>
-      <c r="E183" t="s">
-        <v>312</v>
-      </c>
-      <c r="F183" t="s">
-        <v>186</v>
+        <v>250</v>
       </c>
       <c r="H183" s="3"/>
-      <c r="L183" t="s">
-        <v>313</v>
-      </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A184" s="3" t="s">
-        <v>112</v>
+        <v>40</v>
       </c>
       <c r="B184" t="s">
-        <v>121</v>
-      </c>
-      <c r="H184" s="3" t="s">
-        <v>20</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="H184" s="3"/>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A185" s="3" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="B185" t="s">
-        <v>122</v>
-      </c>
-      <c r="H185" s="3"/>
+        <v>117</v>
+      </c>
+      <c r="D185" t="s">
+        <v>209</v>
+      </c>
+      <c r="E185" t="s">
+        <v>290</v>
+      </c>
+      <c r="H185" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A186" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="B186" t="s">
-        <v>123</v>
+        <v>118</v>
+      </c>
+      <c r="D186" t="s">
+        <v>210</v>
+      </c>
+      <c r="E186" t="s">
+        <v>291</v>
+      </c>
+      <c r="F186" t="s">
+        <v>173</v>
       </c>
       <c r="H186" s="3"/>
+      <c r="L186" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A187" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="B187" t="s">
-        <v>269</v>
-      </c>
-      <c r="H187" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="H187" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A188" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B188" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H188" s="3"/>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A189" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="B189" t="s">
-        <v>125</v>
-      </c>
-      <c r="H189" s="3" t="s">
-        <v>20</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="H189" s="3"/>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A190" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="B190" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="H190" s="3"/>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A191" s="3" t="s">
-        <v>126</v>
+        <v>14</v>
       </c>
       <c r="B191" t="s">
-        <v>125</v>
-      </c>
-      <c r="H191" s="3" t="s">
-        <v>17</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="H191" s="3"/>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A192" s="3" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="B192" t="s">
-        <v>127</v>
+        <v>123</v>
+      </c>
+      <c r="H192" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A193" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="B193" t="s">
-        <v>271</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="H193" s="3"/>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A194" s="3" t="s">
+        <v>124</v>
+      </c>
       <c r="B194" t="s">
-        <v>128</v>
-      </c>
-      <c r="L194" t="s">
-        <v>313</v>
+        <v>123</v>
+      </c>
+      <c r="H194" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A195" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="B195" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B196" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A197" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="B197" t="s">
-        <v>130</v>
+        <v>126</v>
+      </c>
+      <c r="L197" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A198" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="B198" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A199" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="B199" t="s">
-        <v>132</v>
+        <v>311</v>
+      </c>
+      <c r="D199" t="s">
+        <v>210</v>
+      </c>
+      <c r="E199" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A200" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B200" t="s">
-        <v>133</v>
+        <v>312</v>
+      </c>
+      <c r="D200" t="s">
+        <v>194</v>
+      </c>
+      <c r="E200" t="s">
+        <v>290</v>
+      </c>
+      <c r="F200" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A201" s="3" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B201" t="s">
-        <v>224</v>
-      </c>
-      <c r="D201" t="s">
-        <v>223</v>
-      </c>
-      <c r="F201" t="s">
-        <v>186</v>
+        <v>128</v>
       </c>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.2">
@@ -3741,116 +3762,95 @@
         <v>14</v>
       </c>
       <c r="B202" t="s">
-        <v>225</v>
-      </c>
-      <c r="D202" t="s">
-        <v>226</v>
-      </c>
-      <c r="F202" t="s">
-        <v>190</v>
+        <v>315</v>
       </c>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A203" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B203" t="s">
-        <v>134</v>
-      </c>
-      <c r="D203" t="s">
-        <v>226</v>
+        <v>313</v>
       </c>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A204" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B204" t="s">
-        <v>135</v>
-      </c>
-      <c r="D204" t="s">
-        <v>207</v>
-      </c>
-      <c r="E204" t="s">
-        <v>312</v>
-      </c>
-      <c r="F204" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A205" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B205" t="s">
-        <v>136</v>
-      </c>
-      <c r="E205" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A206" s="3" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B206" t="s">
-        <v>137</v>
+        <v>317</v>
       </c>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A207" s="3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B207" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A208" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B208" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A209" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B209" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A210" s="3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B210" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A211" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B211" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A212" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B212" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A213" s="3" t="s">
-        <v>199</v>
+        <v>20</v>
       </c>
       <c r="B213" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.2">
@@ -3858,31 +3858,31 @@
         <v>17</v>
       </c>
       <c r="B214" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A215" s="3" t="s">
-        <v>14</v>
+        <v>186</v>
       </c>
       <c r="B215" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A216" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B216" t="s">
-        <v>273</v>
+        <v>138</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A217" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B217" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.2">
@@ -3890,7 +3890,7 @@
         <v>20</v>
       </c>
       <c r="B218" t="s">
-        <v>148</v>
+        <v>255</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.2">
@@ -3898,15 +3898,15 @@
         <v>17</v>
       </c>
       <c r="B219" t="s">
-        <v>149</v>
+        <v>318</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A220" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B220" t="s">
-        <v>150</v>
+        <v>319</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.2">
@@ -3914,7 +3914,7 @@
         <v>22</v>
       </c>
       <c r="B221" t="s">
-        <v>151</v>
+        <v>320</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.2">
@@ -3922,23 +3922,23 @@
         <v>20</v>
       </c>
       <c r="B222" t="s">
-        <v>152</v>
+        <v>321</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A223" s="3" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B223" t="s">
-        <v>274</v>
+        <v>140</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A224" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B224" t="s">
-        <v>275</v>
+        <v>322</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.2">
@@ -3946,156 +3946,153 @@
         <v>14</v>
       </c>
       <c r="B225" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A226" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="B226" t="s">
-        <v>277</v>
-      </c>
-      <c r="D226" t="s">
-        <v>207</v>
-      </c>
-      <c r="E226" t="s">
-        <v>311</v>
+        <v>256</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A227" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="B227" t="s">
-        <v>153</v>
-      </c>
-      <c r="D227" t="s">
-        <v>216</v>
-      </c>
-      <c r="E227" t="s">
-        <v>288</v>
-      </c>
-      <c r="F227" t="s">
-        <v>190</v>
+        <v>257</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B228" t="s">
-        <v>278</v>
+        <v>324</v>
+      </c>
+      <c r="D228" t="s">
+        <v>194</v>
+      </c>
+      <c r="E228" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B229" t="s">
-        <v>154</v>
+        <v>141</v>
+      </c>
+      <c r="D229" t="s">
+        <v>203</v>
+      </c>
+      <c r="E229" t="s">
+        <v>268</v>
+      </c>
+      <c r="F229" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A230" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="B230" t="s">
-        <v>279</v>
+        <v>258</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A231" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="B231" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A232" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B232" t="s">
-        <v>280</v>
+        <v>259</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A233" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B233" t="s">
-        <v>281</v>
+        <v>143</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A234" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="B234" t="s">
-        <v>156</v>
+        <v>260</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A235" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="B235" t="s">
-        <v>157</v>
+        <v>261</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A236" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="B236" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A237" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="B237" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A238" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="B238" t="s">
-        <v>159</v>
+        <v>325</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A239" s="3" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B239" t="s">
-        <v>160</v>
+        <v>326</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A240" s="3" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B240" t="s">
-        <v>161</v>
+        <v>327</v>
       </c>
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A241" s="3" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B241" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
     </row>
     <row r="242" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A242" s="3" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B242" t="s">
-        <v>282</v>
+        <v>147</v>
       </c>
     </row>
     <row r="243" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A243" s="3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B243" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A244" s="3" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B244" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.2">
@@ -4103,23 +4100,23 @@
         <v>17</v>
       </c>
       <c r="B245" t="s">
-        <v>283</v>
+        <v>262</v>
       </c>
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A246" s="3" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B246" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
     </row>
     <row r="247" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A247" s="3" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B247" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.2">
@@ -4127,127 +4124,151 @@
         <v>17</v>
       </c>
       <c r="B248" t="s">
-        <v>167</v>
+        <v>263</v>
       </c>
     </row>
     <row r="249" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A249" s="3" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B249" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A250" s="3" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B250" t="s">
-        <v>284</v>
+        <v>153</v>
       </c>
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A251" s="3" t="s">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c r="B251" t="s">
-        <v>204</v>
-      </c>
-      <c r="C251" t="s">
-        <v>227</v>
-      </c>
-      <c r="L251" t="s">
-        <v>289</v>
+        <v>154</v>
       </c>
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A252" s="3" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B252" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A253" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B253" t="s">
-        <v>171</v>
+        <v>264</v>
       </c>
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A254" s="3" t="s">
-        <v>17</v>
+        <v>156</v>
       </c>
       <c r="B254" t="s">
-        <v>172</v>
+        <v>191</v>
+      </c>
+      <c r="C254" t="s">
+        <v>211</v>
+      </c>
+      <c r="L254" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A255" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B255" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A256" s="3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B256" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A257" s="3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B257" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A258" s="3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B258" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A259" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="B259" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A260" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="B260" t="s">
-        <v>178</v>
-      </c>
-      <c r="D260" t="s">
-        <v>216</v>
+        <v>162</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A261" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="B261" t="s">
-        <v>228</v>
-      </c>
-      <c r="D261" t="s">
-        <v>182</v>
+        <v>163</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A262" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="B262" t="s">
-        <v>229</v>
+        <v>164</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="L263" t="s">
-        <v>179</v>
+      <c r="B263" t="s">
+        <v>165</v>
+      </c>
+      <c r="D263" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="264" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B264" t="s">
+        <v>212</v>
+      </c>
+      <c r="D264" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="265" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A265" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B265" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="266" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L266" t="s">
+        <v>166</v>
       </c>
     </row>
   </sheetData>
